--- a/outputs/9391.xlsx
+++ b/outputs/9391.xlsx
@@ -145,20 +145,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -357,194 +361,194 @@
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="1" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="n">
         <v>42549</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" s="2" t="n">
         <v>42550</v>
       </c>
-      <c r="D1" s="2" t="n">
+      <c r="D1" s="3" t="n">
         <v>42551</v>
       </c>
-      <c r="E1" s="2" t="n">
+      <c r="E1" s="3" t="n">
         <v>42552</v>
       </c>
-      <c r="F1" s="2" t="n">
+      <c r="F1" s="3" t="n">
         <v>42553</v>
       </c>
-      <c r="G1" s="2" t="n">
+      <c r="G1" s="3" t="n">
         <v>42554</v>
       </c>
-      <c r="H1" s="2" t="n">
+      <c r="H1" s="3" t="n">
         <v>42555</v>
       </c>
-      <c r="I1" s="2" t="n">
+      <c r="I1" s="3" t="n">
         <v>42556</v>
       </c>
-      <c r="J1" s="2" t="n">
+      <c r="J1" s="3" t="n">
         <v>42557</v>
       </c>
-      <c r="K1" s="2" t="n">
+      <c r="K1" s="3" t="n">
         <v>42558</v>
       </c>
-      <c r="L1" s="2" t="n">
+      <c r="L1" s="3" t="n">
         <v>42559</v>
       </c>
-      <c r="M1" s="2" t="n">
+      <c r="M1" s="3" t="n">
         <v>42560</v>
       </c>
-      <c r="N1" s="2" t="n">
+      <c r="N1" s="3" t="n">
         <v>42561</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A2,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B2" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A2,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>2219</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A2,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C2" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A2,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1738</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A3,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B3" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A3,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>2285</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A3,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C3" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A3,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1034</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A4,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B4" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A4,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1804</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A4,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C4" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A4,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A5,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B5" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A5,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1830</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A5,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C5" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A5,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1580</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A6,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B6" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A6,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>835</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A6,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C6" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A6,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A7,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A7,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B7" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A7,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A7,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>15242</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A8,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B8" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A8,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1580</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A8,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C8" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A8,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>835</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A9,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A9,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B9" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A9,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A9,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1830</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A10,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B10" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A10,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1034</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A10,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C10" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A10,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1804</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A11,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B11" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A11,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1738</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A11,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C11" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A11,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>2285</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,B$1)=0,"",INDEX(Data!$F:$F,MATCH(B$1,Data!$A:$A,0)+2+MATCH($A12,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="B12" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(B$1,Data!$A:$A,0)+3+MATCH($A12,INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(B$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>1917</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <f aca="false">IF(COUNTIF(Data!$A:$A,C$1)=0,"",INDEX(Data!$F:$F,MATCH(C$1,Data!$A:$A,0)+2+MATCH($A12,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)))</f>
+      <c r="C12" s="1" t="n">
+        <f aca="false">IFERROR(INDEX(Data!$F:$F, MATCH(C$1,Data!$A:$A,0)+3+MATCH($A12,INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+3):INDEX(Data!$A:$A,MATCH(C$1,Data!$A:$A,0)+13),0)-1),"")</f>
         <v>2219</v>
       </c>
     </row>
@@ -567,1180 +571,1180 @@
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="n">
+      <c r="A1" s="3" t="n">
         <v>42549</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="1" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>302891</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>171849</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>38632</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>15242</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>28799</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>69810</v>
       </c>
-      <c r="I3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="0" t="n">
+      <c r="I3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>18252</v>
       </c>
-      <c r="K3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="0" t="n">
+      <c r="K3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="M3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="0" t="n">
+      <c r="M3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1" t="n">
         <v>744</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>30733</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>13680</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>3001</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>2219</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>3886</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="0" t="n">
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>4574</v>
       </c>
-      <c r="K4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="0" t="n">
+      <c r="K4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>30522</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>16455</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>4549</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>2285</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="n">
+      <c r="G5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>9621</v>
       </c>
-      <c r="I5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="0" t="n">
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>30807</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>13115</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>4280</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>1804</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>3537</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>2605</v>
       </c>
-      <c r="I6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0" t="n">
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="M6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="0" t="n">
+      <c r="M6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>722</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>31042</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>12601</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>2941</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>1830</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>3625</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>4183</v>
       </c>
-      <c r="I7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="0" t="n">
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>33047</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>33047</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>8730</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>835</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>1831</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>7973</v>
       </c>
-      <c r="I8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="0" t="n">
+      <c r="I8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="n">
         <v>13678</v>
       </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="0" t="n">
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="0" t="n">
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>31319</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>17642</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>3471</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>1580</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>3388</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>9000</v>
       </c>
-      <c r="I10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="n">
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="n">
         <v>203</v>
       </c>
-      <c r="M10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="0" t="n">
+      <c r="M10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>31144</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>19360</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>4884</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="0" t="n">
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <v>14476</v>
       </c>
-      <c r="I11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="0" t="n">
+      <c r="I11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>21922</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>13880</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>1420</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
         <v>1034</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>5355</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>6071</v>
       </c>
-      <c r="I12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="0" t="n">
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>30532</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>17909</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>4155</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="4" t="n">
         <v>1738</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>3664</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <v>8352</v>
       </c>
-      <c r="I13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="0" t="n">
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>31594</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>13931</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>972</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>1917</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <v>3513</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <v>7529</v>
       </c>
-      <c r="I14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="0" t="n">
+      <c r="I14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>42550</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O17" s="1" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>302891</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <v>171849</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>38632</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <v>1917</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="1" t="n">
         <v>28799</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="1" t="n">
         <v>69810</v>
       </c>
-      <c r="I18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="0" t="n">
+      <c r="I18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="n">
         <v>18252</v>
       </c>
-      <c r="K18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="0" t="n">
+      <c r="K18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="M18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="0" t="n">
+      <c r="M18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1" t="n">
         <v>744</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>30733</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <v>13680</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <v>3001</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="4" t="n">
         <v>1738</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="1" t="n">
         <v>3886</v>
       </c>
-      <c r="H19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="0" t="n">
+      <c r="H19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="n">
         <v>4574</v>
       </c>
-      <c r="K19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="0" t="n">
+      <c r="K19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>30522</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <v>16455</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <v>4549</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="4" t="n">
         <v>1034</v>
       </c>
-      <c r="G20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="0" t="n">
+      <c r="G20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="n">
         <v>9621</v>
       </c>
-      <c r="I20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="0" t="n">
+      <c r="I20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="1" t="n">
         <v>30807</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <v>13115</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <v>4280</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="0" t="n">
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>3537</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="1" t="n">
         <v>2605</v>
       </c>
-      <c r="I21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="0" t="n">
+      <c r="I21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="M21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="0" t="n">
+      <c r="M21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>722</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="1" t="n">
         <v>31042</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D22" s="1" t="n">
         <v>12601</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="1" t="n">
         <v>2941</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="4" t="n">
         <v>1580</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="G22" s="1" t="n">
         <v>3625</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="1" t="n">
         <v>4183</v>
       </c>
-      <c r="I22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="0" t="n">
+      <c r="I22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="1" t="n">
         <v>33047</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="1" t="n">
         <v>33047</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <v>8730</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="0" t="n">
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>1831</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="1" t="n">
         <v>7973</v>
       </c>
-      <c r="I23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="0" t="n">
+      <c r="I23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="n">
         <v>13678</v>
       </c>
-      <c r="K23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="0" t="n">
+      <c r="K23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="4" t="n">
         <v>15242</v>
       </c>
-      <c r="G24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="0" t="n">
+      <c r="G24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>31319</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25" s="1" t="n">
         <v>17642</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <v>3471</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="4" t="n">
         <v>835</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25" s="1" t="n">
         <v>3388</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="1" t="n">
         <v>9000</v>
       </c>
-      <c r="I25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="0" t="n">
+      <c r="I25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1" t="n">
         <v>203</v>
       </c>
-      <c r="M25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="0" t="n">
+      <c r="M25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="1" t="n">
         <v>31144</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="1" t="n">
         <v>19360</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="1" t="n">
         <v>4884</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="4" t="n">
         <v>1830</v>
       </c>
-      <c r="G26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="0" t="n">
+      <c r="G26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="n">
         <v>14476</v>
       </c>
-      <c r="I26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="0" t="n">
+      <c r="I26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="1" t="n">
         <v>21922</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="1" t="n">
         <v>13880</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <v>1420</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="4" t="n">
         <v>1804</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27" s="1" t="n">
         <v>5355</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="1" t="n">
         <v>6071</v>
       </c>
-      <c r="I27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="0" t="n">
+      <c r="I27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="1" t="n">
         <v>30532</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="1" t="n">
         <v>17909</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="1" t="n">
         <v>4155</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="4" t="n">
         <v>2285</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="1" t="n">
         <v>3664</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="1" t="n">
         <v>8352</v>
       </c>
-      <c r="I28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="0" t="n">
+      <c r="I28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="1" t="n">
         <v>31594</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="1" t="n">
         <v>13931</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="1" t="n">
         <v>972</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="4" t="n">
         <v>2219</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G29" s="1" t="n">
         <v>3513</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="1" t="n">
         <v>7529</v>
       </c>
-      <c r="I29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="0" t="n">
+      <c r="I29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="n">
         <v>0</v>
       </c>
     </row>
